--- a/data/invoices/totals.xlsx
+++ b/data/invoices/totals.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44699A60-A91B-423C-9E01-14CA1A1CAB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3A137A-7D22-40E5-B107-8A04B25977F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -176,9 +176,6 @@
     <t>2026-06-19</t>
   </si>
   <si>
-    <t>اسكيمو للهندسه والتجاره رقم الفاتوره 26.pdf</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -686,27 +683,18 @@
     <t>34412</t>
   </si>
   <si>
-    <t>الرومانى رقم الفاتوره 24306.pdf</t>
-  </si>
-  <si>
     <t>24306</t>
   </si>
   <si>
     <t>305357395</t>
   </si>
   <si>
-    <t>الرومانى رقم الفاتوره 24592.pdf</t>
-  </si>
-  <si>
     <t>24592</t>
   </si>
   <si>
     <t>2026-05-13</t>
   </si>
   <si>
-    <t>الرومانى رقم الفاتوره 24600.pdf</t>
-  </si>
-  <si>
     <t>24600</t>
   </si>
   <si>
@@ -1787,27 +1775,18 @@
     <t>100127908</t>
   </si>
   <si>
-    <t>دنيا العوازل رقم الفاتوره 12.pdf</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
     <t>438299779</t>
   </si>
   <si>
-    <t>دنيا العوازل رقم الفاتوره 141.pdf</t>
-  </si>
-  <si>
     <t>141</t>
   </si>
   <si>
     <t>2026-04-29</t>
   </si>
   <si>
-    <t>دنيا العوازل رقم الفاتوره 60.pdf</t>
-  </si>
-  <si>
     <t>60</t>
   </si>
   <si>
@@ -2222,75 +2201,39 @@
     <t>2026-05-04</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتور 3.pdf</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتوره 10.pdf</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتوره 14.pdf</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتوره 16.pdf</t>
-  </si>
-  <si>
     <t>16</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتوره 2.pdf</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتوره 20.pdf</t>
-  </si>
-  <si>
     <t>20</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتوره 23.pdf</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتوره 24.pdf</t>
-  </si>
-  <si>
     <t>24</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتوره 27.pdf</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتوره 8.pdf</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتوره 85.pdf</t>
-  </si>
-  <si>
     <t>85</t>
   </si>
   <si>
-    <t>مارن اثا رقم الفاتوره 9.pdf</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
@@ -2312,9 +2255,6 @@
     <t>449751112</t>
   </si>
   <si>
-    <t>مدينة كنوز مصر للروخام رقم الفاتوره 706.pdf</t>
-  </si>
-  <si>
     <t>723554765</t>
   </si>
   <si>
@@ -2532,13 +2472,73 @@
   </si>
   <si>
     <t>اجمالي المشتريات (ج.م)</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتور 3.pdf</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتوره 2.pdf</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتوره 10.pdf</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتوره 8.pdf</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتوره 9.pdf</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتوره 14.pdf</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتوره 16.pdf</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتوره 20.pdf</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتوره 23.pdf</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتوره 24.pdf</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتوره 27.pdf</t>
+  </si>
+  <si>
+    <t>ماران اثا رقم الفاتوره 85.pdf</t>
+  </si>
+  <si>
+    <t>اسكيمو للهندسه رقم الفاتوره 26.pdf</t>
+  </si>
+  <si>
+    <t>دنيا العوازال رقم الفاتوره 12.pdf</t>
+  </si>
+  <si>
+    <t>دنيا العوازال رقم الفاتوره 60.pdf</t>
+  </si>
+  <si>
+    <t>دنيا العوازال رقم الفاتوره 141.pdf</t>
+  </si>
+  <si>
+    <t>الروماني رقم الفاتوره 24306.pdf</t>
+  </si>
+  <si>
+    <t>الروماني رقم الفاتوره 24592.pdf</t>
+  </si>
+  <si>
+    <t>الروماني رقم الفاتوره 24600.pdf</t>
+  </si>
+  <si>
+    <t>مدينة كنوز مصر للرخام رقم الفاتوره 706.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3010,7 +3010,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I326"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -3020,7 +3020,7 @@
     <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="27.95" customHeight="1">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>834</v>
+        <v>814</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -3049,12 +3049,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="3" customFormat="1">
+    <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="C2" s="14">
         <v>46131</v>
@@ -3080,18 +3080,18 @@
         <v>606113.83200000005</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="3" customFormat="1">
+    <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>761</v>
+        <v>834</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C3" s="14">
         <v>46022</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>762</v>
+        <v>742</v>
       </c>
       <c r="E3" s="4">
         <v>14468</v>
@@ -3109,18 +3109,18 @@
         <v>16493.52</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="3" customFormat="1">
+    <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E4" s="4">
         <v>6775</v>
@@ -3138,18 +3138,18 @@
         <v>7723.5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="3" customFormat="1">
+    <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E5" s="7">
         <v>31756.14</v>
@@ -3167,18 +3167,18 @@
         <v>36202</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="3" customFormat="1">
+    <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>814</v>
+        <v>794</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>815</v>
+        <v>795</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>816</v>
+        <v>796</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E6" s="4">
         <v>840</v>
@@ -3196,18 +3196,18 @@
         <v>949.2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="3" customFormat="1">
+    <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" s="4">
         <v>368953.59999999998</v>
@@ -3225,18 +3225,18 @@
         <v>416917.56800000003</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="3" customFormat="1">
+    <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="E8" s="4">
         <v>31875</v>
@@ -3254,18 +3254,18 @@
         <v>36337.5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="3" customFormat="1">
+    <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E9" s="7">
         <v>33040</v>
@@ -3283,18 +3283,18 @@
         <v>37335.199999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="3" customFormat="1">
+    <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>161</v>
-      </c>
       <c r="D10" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E10" s="7">
         <v>27000</v>
@@ -3312,18 +3312,18 @@
         <v>30780</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="3" customFormat="1">
+    <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>68</v>
-      </c>
       <c r="D11" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" s="7">
         <v>110394.94</v>
@@ -3341,18 +3341,18 @@
         <v>124746.2822</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="3" customFormat="1">
+    <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E12" s="4">
         <v>3090</v>
@@ -3370,18 +3370,18 @@
         <v>3491.7</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="3" customFormat="1">
+    <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E13" s="4">
         <v>74605</v>
@@ -3399,18 +3399,18 @@
         <v>84303.65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="3" customFormat="1">
+    <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E14" s="4">
         <v>123000</v>
@@ -3428,7 +3428,7 @@
         <v>140220</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="3" customFormat="1">
+    <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>16</v>
       </c>
@@ -3457,18 +3457,18 @@
         <v>29380</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="3" customFormat="1">
+    <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E16" s="4">
         <v>5000</v>
@@ -3486,18 +3486,18 @@
         <v>5650</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="3" customFormat="1">
+    <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>219</v>
+        <v>831</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E17" s="7">
         <v>8100</v>
@@ -3515,18 +3515,18 @@
         <v>9153</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="3" customFormat="1">
+    <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E18" s="4">
         <v>4350</v>
@@ -3544,18 +3544,18 @@
         <v>4959</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="3" customFormat="1">
+    <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E19" s="4">
         <v>23550</v>
@@ -3573,18 +3573,18 @@
         <v>26611.5</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="3" customFormat="1">
+    <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E20" s="7">
         <v>110616.54</v>
@@ -3602,18 +3602,18 @@
         <v>124996.6902</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="3" customFormat="1">
+    <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>586</v>
+        <v>828</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E21" s="7">
         <v>7250</v>
@@ -3631,18 +3631,18 @@
         <v>8265</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="3" customFormat="1">
+    <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>731</v>
+        <v>815</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E22" s="7">
         <v>30787.5</v>
@@ -3660,18 +3660,18 @@
         <v>35097.75</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="3" customFormat="1">
+    <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>739</v>
+        <v>816</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E23" s="7">
         <v>8725</v>
@@ -3689,18 +3689,18 @@
         <v>9946.5</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="3" customFormat="1">
+    <row r="24" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="D24" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E24" s="7">
         <v>70500</v>
@@ -3718,18 +3718,18 @@
         <v>80370</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="3" customFormat="1">
+    <row r="25" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>166</v>
-      </c>
       <c r="C25" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E25" s="7">
         <v>75000</v>
@@ -3747,18 +3747,18 @@
         <v>85500</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="3" customFormat="1">
+    <row r="26" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="C26" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="E26" s="7">
         <v>12500</v>
@@ -3776,18 +3776,18 @@
         <v>14125</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="3" customFormat="1">
+    <row r="27" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E27" s="4">
         <v>6750</v>
@@ -3805,18 +3805,18 @@
         <v>7627.5</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="3" customFormat="1">
+    <row r="28" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E28" s="4">
         <v>55620</v>
@@ -3834,18 +3834,18 @@
         <v>62850.6</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="3" customFormat="1">
+    <row r="29" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="E29" s="7">
         <v>31625</v>
@@ -3863,18 +3863,18 @@
         <v>36052.5</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="3" customFormat="1">
+    <row r="30" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>733</v>
+        <v>817</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E30" s="4">
         <v>9935</v>
@@ -3892,18 +3892,18 @@
         <v>11325.9</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="3" customFormat="1">
+    <row r="31" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>749</v>
+        <v>818</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>750</v>
+        <v>733</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E31" s="4">
         <v>238423.57</v>
@@ -3921,18 +3921,18 @@
         <v>271802.86979999999</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="3" customFormat="1">
+    <row r="32" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>753</v>
+        <v>819</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E32" s="4">
         <v>18929.25</v>
@@ -3950,18 +3950,18 @@
         <v>21579.345000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="3" customFormat="1">
+    <row r="33" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E33" s="7">
         <v>12325</v>
@@ -3979,18 +3979,18 @@
         <v>13927.25</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="3" customFormat="1">
+    <row r="34" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E34" s="7">
         <v>2500</v>
@@ -4008,18 +4008,18 @@
         <v>2825</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="3" customFormat="1">
+    <row r="35" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="C35" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>200</v>
-      </c>
       <c r="D35" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E35" s="7">
         <v>5000</v>
@@ -4037,18 +4037,18 @@
         <v>5650</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="3" customFormat="1">
+    <row r="36" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E36" s="4">
         <v>2400</v>
@@ -4066,18 +4066,18 @@
         <v>2712</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="3" customFormat="1">
+    <row r="37" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E37" s="7">
         <v>17500</v>
@@ -4095,18 +4095,18 @@
         <v>19950</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="3" customFormat="1">
+    <row r="38" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E38" s="4">
         <v>8250</v>
@@ -4124,18 +4124,18 @@
         <v>9322.5</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="3" customFormat="1">
+    <row r="39" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E39" s="7">
         <v>37544.519999999997</v>
@@ -4153,18 +4153,18 @@
         <v>42800.76</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="3" customFormat="1">
+    <row r="40" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>735</v>
+        <v>820</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E40" s="7">
         <v>25977.55</v>
@@ -4182,18 +4182,18 @@
         <v>29614.406999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="3" customFormat="1">
+    <row r="41" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E41" s="4">
         <v>83220</v>
@@ -4211,18 +4211,18 @@
         <v>94038.6</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="3" customFormat="1">
+    <row r="42" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="C42" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E42" s="4">
         <v>37500</v>
@@ -4240,18 +4240,18 @@
         <v>42750</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="3" customFormat="1">
+    <row r="43" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E43" s="4">
         <v>31500</v>
@@ -4269,18 +4269,18 @@
         <v>35595</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="3" customFormat="1">
+    <row r="44" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E44" s="7">
         <v>15850</v>
@@ -4298,18 +4298,18 @@
         <v>17910.5</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="3" customFormat="1">
+    <row r="45" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="E45" s="7">
         <v>1315</v>
@@ -4327,18 +4327,18 @@
         <v>1499.1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="3" customFormat="1">
+    <row r="46" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>737</v>
+        <v>821</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E46" s="4">
         <v>10795.8</v>
@@ -4356,18 +4356,18 @@
         <v>12307.212</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="3" customFormat="1">
+    <row r="47" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="C47" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="D47" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="E47" s="7">
         <v>235708</v>
@@ -4385,18 +4385,18 @@
         <v>266350.03999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="3" customFormat="1">
+    <row r="48" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E48" s="7">
         <v>36000</v>
@@ -4414,18 +4414,18 @@
         <v>41040</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="3" customFormat="1">
+    <row r="49" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>792</v>
+        <v>772</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>793</v>
+        <v>773</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E49" s="7">
         <v>22125</v>
@@ -4443,18 +4443,18 @@
         <v>25001.25</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="3" customFormat="1">
+    <row r="50" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E50" s="7">
         <v>8116.8</v>
@@ -4472,18 +4472,18 @@
         <v>9253.152</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="3" customFormat="1">
+    <row r="51" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D51" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E51" s="4">
         <v>11880</v>
@@ -4501,18 +4501,18 @@
         <v>13543.2</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="3" customFormat="1">
+    <row r="52" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="C52" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E52" s="7">
         <v>68510</v>
@@ -4530,18 +4530,18 @@
         <v>77416.3</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="3" customFormat="1">
+    <row r="53" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E53" s="7">
         <v>1785</v>
@@ -4559,18 +4559,18 @@
         <v>2017.05</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="3" customFormat="1">
+    <row r="54" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E54" s="7">
         <v>1443</v>
@@ -4588,18 +4588,18 @@
         <v>1645.02</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="3" customFormat="1">
+    <row r="55" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E55" s="7">
         <v>637964.03200000001</v>
@@ -4617,18 +4617,18 @@
         <v>727278.99699999997</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="3" customFormat="1">
+    <row r="56" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="D56" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E56" s="4">
         <v>1800</v>
@@ -4646,18 +4646,18 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="3" customFormat="1">
+    <row r="57" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E57" s="7">
         <v>247501.21</v>
@@ -4675,18 +4675,18 @@
         <v>279676.36729999998</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="3" customFormat="1">
+    <row r="58" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="C58" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>171</v>
-      </c>
       <c r="D58" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E58" s="7">
         <v>10800</v>
@@ -4704,18 +4704,18 @@
         <v>12312</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="3" customFormat="1">
+    <row r="59" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="C59" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E59" s="4">
         <v>11500</v>
@@ -4733,18 +4733,18 @@
         <v>12995</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="3" customFormat="1">
+    <row r="60" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E60" s="4">
         <v>9800</v>
@@ -4762,18 +4762,18 @@
         <v>11172</v>
       </c>
     </row>
-    <row r="61" spans="1:9" s="3" customFormat="1">
+    <row r="61" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E61" s="7">
         <v>2581</v>
@@ -4791,18 +4791,18 @@
         <v>2942.34</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="3" customFormat="1">
+    <row r="62" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>741</v>
+        <v>822</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E62" s="4">
         <v>13184.5</v>
@@ -4820,18 +4820,18 @@
         <v>15030.33</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="3" customFormat="1">
+    <row r="63" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>755</v>
+        <v>736</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>756</v>
+        <v>737</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="E63" s="7">
         <v>25400</v>
@@ -4849,18 +4849,18 @@
         <v>28956</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="3" customFormat="1">
+    <row r="64" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E64" s="4">
         <v>507985</v>
@@ -4878,7 +4878,7 @@
         <v>574023.05000000005</v>
       </c>
     </row>
-    <row r="65" spans="1:9" s="3" customFormat="1">
+    <row r="65" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>11</v>
       </c>
@@ -4907,18 +4907,18 @@
         <v>29434.799999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:9" s="3" customFormat="1">
+    <row r="66" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E66" s="4">
         <v>25400</v>
@@ -4936,18 +4936,18 @@
         <v>28956</v>
       </c>
     </row>
-    <row r="67" spans="1:9" s="3" customFormat="1">
+    <row r="67" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E67" s="4">
         <v>2050</v>
@@ -4965,7 +4965,7 @@
         <v>2316.5</v>
       </c>
     </row>
-    <row r="68" spans="1:9" s="3" customFormat="1">
+    <row r="68" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>20</v>
       </c>
@@ -4994,18 +4994,18 @@
         <v>29380</v>
       </c>
     </row>
-    <row r="69" spans="1:9" s="3" customFormat="1">
+    <row r="69" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E69" s="4">
         <v>5250</v>
@@ -5023,18 +5023,18 @@
         <v>5932.5</v>
       </c>
     </row>
-    <row r="70" spans="1:9" s="3" customFormat="1">
+    <row r="70" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E70" s="4">
         <v>114000</v>
@@ -5052,18 +5052,18 @@
         <v>128820</v>
       </c>
     </row>
-    <row r="71" spans="1:9" s="3" customFormat="1">
+    <row r="71" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>795</v>
+        <v>775</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>796</v>
+        <v>776</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E71" s="4">
         <v>600</v>
@@ -5081,18 +5081,18 @@
         <v>678</v>
       </c>
     </row>
-    <row r="72" spans="1:9" s="3" customFormat="1">
+    <row r="72" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="C72" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C72" s="6" t="s">
-        <v>189</v>
-      </c>
       <c r="D72" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E72" s="7">
         <v>18750</v>
@@ -5110,18 +5110,18 @@
         <v>21375</v>
       </c>
     </row>
-    <row r="73" spans="1:9" s="3" customFormat="1">
+    <row r="73" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="E73" s="7">
         <v>1991.2280000000001</v>
@@ -5139,18 +5139,18 @@
         <v>2269.9999200000002</v>
       </c>
     </row>
-    <row r="74" spans="1:9" s="3" customFormat="1">
+    <row r="74" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="D74" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E74" s="4">
         <v>126996</v>
@@ -5168,18 +5168,18 @@
         <v>143505.48000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:9" s="3" customFormat="1">
+    <row r="75" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>743</v>
+        <v>823</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E75" s="7">
         <v>30829.5</v>
@@ -5197,18 +5197,18 @@
         <v>35145.629999999997</v>
       </c>
     </row>
-    <row r="76" spans="1:9" s="3" customFormat="1">
+    <row r="76" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>745</v>
+        <v>824</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>746</v>
+        <v>731</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E76" s="4">
         <v>36539.550000000003</v>
@@ -5226,18 +5226,18 @@
         <v>41655.087</v>
       </c>
     </row>
-    <row r="77" spans="1:9" s="3" customFormat="1">
+    <row r="77" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E77" s="7">
         <v>12800</v>
@@ -5255,18 +5255,18 @@
         <v>14464</v>
       </c>
     </row>
-    <row r="78" spans="1:9" s="3" customFormat="1">
+    <row r="78" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="D78" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E78" s="4">
         <v>1525</v>
@@ -5284,18 +5284,18 @@
         <v>1738.5</v>
       </c>
     </row>
-    <row r="79" spans="1:9" s="3" customFormat="1">
+    <row r="79" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="E79" s="4">
         <v>1370</v>
@@ -5313,18 +5313,18 @@
         <v>1561.8</v>
       </c>
     </row>
-    <row r="80" spans="1:9" s="3" customFormat="1">
+    <row r="80" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>747</v>
+        <v>825</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E80" s="7">
         <v>6750</v>
@@ -5342,15 +5342,15 @@
         <v>7695</v>
       </c>
     </row>
-    <row r="81" spans="1:9" s="3" customFormat="1">
+    <row r="81" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>32</v>
@@ -5371,18 +5371,18 @@
         <v>203849.32800000001</v>
       </c>
     </row>
-    <row r="82" spans="1:9" s="3" customFormat="1">
+    <row r="82" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="C82" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E82" s="4">
         <v>90980</v>
@@ -5400,18 +5400,18 @@
         <v>100987.8</v>
       </c>
     </row>
-    <row r="83" spans="1:9" s="3" customFormat="1">
+    <row r="83" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>776</v>
+        <v>756</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>777</v>
+        <v>757</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
       <c r="E83" s="7">
         <v>9650</v>
@@ -5429,18 +5429,18 @@
         <v>11001</v>
       </c>
     </row>
-    <row r="84" spans="1:9" s="3" customFormat="1">
+    <row r="84" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E84" s="7">
         <v>10345</v>
@@ -5458,18 +5458,18 @@
         <v>11689.85</v>
       </c>
     </row>
-    <row r="85" spans="1:9" s="3" customFormat="1">
+    <row r="85" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E85" s="4">
         <v>768101.75399999996</v>
@@ -5487,18 +5487,18 @@
         <v>875635.99899999995</v>
       </c>
     </row>
-    <row r="86" spans="1:9" s="3" customFormat="1">
+    <row r="86" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E86" s="4">
         <v>10070</v>
@@ -5516,18 +5516,18 @@
         <v>11379.1</v>
       </c>
     </row>
-    <row r="87" spans="1:9" s="3" customFormat="1">
+    <row r="87" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E87" s="7">
         <v>183870</v>
@@ -5545,18 +5545,18 @@
         <v>182031.3</v>
       </c>
     </row>
-    <row r="88" spans="1:9" s="3" customFormat="1">
+    <row r="88" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>592</v>
+        <v>829</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E88" s="7">
         <v>5535</v>
@@ -5574,18 +5574,18 @@
         <v>6309.9</v>
       </c>
     </row>
-    <row r="89" spans="1:9" s="3" customFormat="1">
+    <row r="89" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B89" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="C89" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="D89" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E89" s="7">
         <v>40125</v>
@@ -5603,18 +5603,18 @@
         <v>45341.25</v>
       </c>
     </row>
-    <row r="90" spans="1:9" s="3" customFormat="1">
+    <row r="90" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E90" s="4">
         <v>12267.54</v>
@@ -5632,7 +5632,7 @@
         <v>13984.993</v>
       </c>
     </row>
-    <row r="91" spans="1:9" s="3" customFormat="1">
+    <row r="91" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>23</v>
       </c>
@@ -5661,18 +5661,18 @@
         <v>118106.47</v>
       </c>
     </row>
-    <row r="92" spans="1:9" s="3" customFormat="1">
+    <row r="92" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E92" s="4">
         <v>22500</v>
@@ -5690,18 +5690,18 @@
         <v>25650</v>
       </c>
     </row>
-    <row r="93" spans="1:9" s="3" customFormat="1">
+    <row r="93" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="E93" s="7">
         <v>525</v>
@@ -5719,18 +5719,18 @@
         <v>598.5</v>
       </c>
     </row>
-    <row r="94" spans="1:9" s="3" customFormat="1">
+    <row r="94" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="D94" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E94" s="4">
         <v>78151.64</v>
@@ -5748,18 +5748,18 @@
         <v>88311.353199999998</v>
       </c>
     </row>
-    <row r="95" spans="1:9" s="3" customFormat="1">
+    <row r="95" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E95" s="4">
         <v>3380</v>
@@ -5777,18 +5777,18 @@
         <v>3819.4</v>
       </c>
     </row>
-    <row r="96" spans="1:9" s="3" customFormat="1">
+    <row r="96" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E96" s="7">
         <v>26305.32</v>
@@ -5806,18 +5806,18 @@
         <v>29988.0648</v>
       </c>
     </row>
-    <row r="97" spans="1:9" s="3" customFormat="1">
+    <row r="97" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E97" s="4">
         <v>3861</v>
@@ -5835,18 +5835,18 @@
         <v>4401.54</v>
       </c>
     </row>
-    <row r="98" spans="1:9" s="3" customFormat="1">
+    <row r="98" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E98" s="7">
         <v>3425</v>
@@ -5864,18 +5864,18 @@
         <v>3904.5</v>
       </c>
     </row>
-    <row r="99" spans="1:9" s="3" customFormat="1">
+    <row r="99" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E99" s="7">
         <v>37544.519999999997</v>
@@ -5893,18 +5893,18 @@
         <v>42800.76</v>
       </c>
     </row>
-    <row r="100" spans="1:9" s="3" customFormat="1">
+    <row r="100" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>797</v>
+        <v>777</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>798</v>
+        <v>778</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E100" s="7">
         <v>2875</v>
@@ -5922,18 +5922,18 @@
         <v>3248.75</v>
       </c>
     </row>
-    <row r="101" spans="1:9" s="3" customFormat="1">
+    <row r="101" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B101" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B101" s="6" t="s">
+      <c r="C101" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>177</v>
-      </c>
       <c r="D101" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E101" s="7">
         <v>15300</v>
@@ -5951,18 +5951,18 @@
         <v>17442</v>
       </c>
     </row>
-    <row r="102" spans="1:9" s="3" customFormat="1">
+    <row r="102" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E102" s="7">
         <v>220026.75</v>
@@ -5980,18 +5980,18 @@
         <v>248630.22750000001</v>
       </c>
     </row>
-    <row r="103" spans="1:9" s="3" customFormat="1">
+    <row r="103" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E103" s="4">
         <v>29794.05</v>
@@ -6009,18 +6009,18 @@
         <v>33965.216999999997</v>
       </c>
     </row>
-    <row r="104" spans="1:9" s="3" customFormat="1">
+    <row r="104" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E104" s="7">
         <v>4199.5</v>
@@ -6038,18 +6038,18 @@
         <v>4787.43</v>
       </c>
     </row>
-    <row r="105" spans="1:9" s="3" customFormat="1">
+    <row r="105" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="C105" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C105" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="D105" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E105" s="4">
         <v>70500</v>
@@ -6067,18 +6067,18 @@
         <v>80370</v>
       </c>
     </row>
-    <row r="106" spans="1:9" s="3" customFormat="1">
+    <row r="106" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E106" s="7">
         <v>83660</v>
@@ -6096,18 +6096,18 @@
         <v>95372.4</v>
       </c>
     </row>
-    <row r="107" spans="1:9" s="3" customFormat="1">
+    <row r="107" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E107" s="4">
         <v>53925</v>
@@ -6125,18 +6125,18 @@
         <v>61474.5</v>
       </c>
     </row>
-    <row r="108" spans="1:9" s="3" customFormat="1">
+    <row r="108" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E108" s="7">
         <v>5000</v>
@@ -6154,18 +6154,18 @@
         <v>5700</v>
       </c>
     </row>
-    <row r="109" spans="1:9" s="3" customFormat="1">
+    <row r="109" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B109" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="C109" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C109" s="6" t="s">
-        <v>205</v>
-      </c>
       <c r="D109" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E109" s="7">
         <v>2100</v>
@@ -6183,18 +6183,18 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="110" spans="1:9" s="3" customFormat="1">
+    <row r="110" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B110" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B110" s="6" t="s">
+      <c r="C110" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C110" s="6" t="s">
-        <v>85</v>
-      </c>
       <c r="D110" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E110" s="7">
         <v>546998.6</v>
@@ -6212,18 +6212,18 @@
         <v>618108.41799999995</v>
       </c>
     </row>
-    <row r="111" spans="1:9" s="3" customFormat="1">
+    <row r="111" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E111" s="7">
         <v>6900</v>
@@ -6241,18 +6241,18 @@
         <v>7797</v>
       </c>
     </row>
-    <row r="112" spans="1:9" s="3" customFormat="1">
+    <row r="112" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E112" s="4">
         <v>18179.75</v>
@@ -6270,18 +6270,18 @@
         <v>20724.919999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:9" s="3" customFormat="1">
+    <row r="113" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E113" s="4">
         <v>25270.51</v>
@@ -6299,18 +6299,18 @@
         <v>28808.381399999998</v>
       </c>
     </row>
-    <row r="114" spans="1:9" s="3" customFormat="1">
+    <row r="114" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>778</v>
+        <v>758</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>779</v>
+        <v>759</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>781</v>
+        <v>761</v>
       </c>
       <c r="E114" s="4">
         <v>17500</v>
@@ -6328,18 +6328,18 @@
         <v>19950</v>
       </c>
     </row>
-    <row r="115" spans="1:9" s="3" customFormat="1">
+    <row r="115" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E115" s="4">
         <v>4335</v>
@@ -6357,18 +6357,18 @@
         <v>4898.55</v>
       </c>
     </row>
-    <row r="116" spans="1:9" s="3" customFormat="1">
+    <row r="116" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E116" s="7">
         <v>22275</v>
@@ -6386,18 +6386,18 @@
         <v>25393.5</v>
       </c>
     </row>
-    <row r="117" spans="1:9" s="3" customFormat="1">
+    <row r="117" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E117" s="7">
         <v>269960</v>
@@ -6415,18 +6415,18 @@
         <v>305054.8</v>
       </c>
     </row>
-    <row r="118" spans="1:9" s="3" customFormat="1">
+    <row r="118" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E118" s="7">
         <v>31156.42</v>
@@ -6444,18 +6444,18 @@
         <v>35518.318800000001</v>
       </c>
     </row>
-    <row r="119" spans="1:9" s="3" customFormat="1">
+    <row r="119" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="C119" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C119" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="D119" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E119" s="4">
         <v>29725</v>
@@ -6473,15 +6473,15 @@
         <v>33886.5</v>
       </c>
     </row>
-    <row r="120" spans="1:9" s="3" customFormat="1">
+    <row r="120" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>765</v>
+        <v>745</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>14</v>
@@ -6502,18 +6502,18 @@
         <v>20930.400000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:9" s="3" customFormat="1">
+    <row r="121" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E121" s="7">
         <v>19255</v>
@@ -6531,18 +6531,18 @@
         <v>21758.15</v>
       </c>
     </row>
-    <row r="122" spans="1:9" s="3" customFormat="1">
+    <row r="122" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E122" s="4">
         <v>8362.16</v>
@@ -6560,18 +6560,18 @@
         <v>9532.8619999999992</v>
       </c>
     </row>
-    <row r="123" spans="1:9" s="3" customFormat="1">
+    <row r="123" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E123" s="4">
         <v>33500</v>
@@ -6589,18 +6589,18 @@
         <v>38190</v>
       </c>
     </row>
-    <row r="124" spans="1:9" s="3" customFormat="1">
+    <row r="124" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E124" s="4">
         <v>139051</v>
@@ -6618,18 +6618,18 @@
         <v>158518.14000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:9" s="3" customFormat="1">
+    <row r="125" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E125" s="7">
         <v>4640</v>
@@ -6647,18 +6647,18 @@
         <v>5289.6</v>
       </c>
     </row>
-    <row r="126" spans="1:9" s="3" customFormat="1">
+    <row r="126" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E126" s="4">
         <v>23475</v>
@@ -6676,18 +6676,18 @@
         <v>26761.5</v>
       </c>
     </row>
-    <row r="127" spans="1:9" s="3" customFormat="1">
+    <row r="127" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E127" s="7">
         <v>17225</v>
@@ -6705,18 +6705,18 @@
         <v>19464.25</v>
       </c>
     </row>
-    <row r="128" spans="1:9" s="3" customFormat="1">
+    <row r="128" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="C128" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C128" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="D128" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E128" s="4">
         <v>53500</v>
@@ -6734,18 +6734,18 @@
         <v>60455</v>
       </c>
     </row>
-    <row r="129" spans="1:9" s="3" customFormat="1">
+    <row r="129" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E129" s="4">
         <v>28754.55</v>
@@ -6763,18 +6763,18 @@
         <v>32780.186999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:9" s="3" customFormat="1">
+    <row r="130" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E130" s="7">
         <v>44226</v>
@@ -6792,18 +6792,18 @@
         <v>50417.64</v>
       </c>
     </row>
-    <row r="131" spans="1:9" s="3" customFormat="1">
+    <row r="131" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E131" s="4">
         <v>9144.08</v>
@@ -6821,18 +6821,18 @@
         <v>9672.6612000000005</v>
       </c>
     </row>
-    <row r="132" spans="1:9" s="3" customFormat="1">
+    <row r="132" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E132" s="7">
         <v>4914</v>
@@ -6850,18 +6850,18 @@
         <v>5601.96</v>
       </c>
     </row>
-    <row r="133" spans="1:9" s="3" customFormat="1">
+    <row r="133" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E133" s="4">
         <v>1660</v>
@@ -6879,18 +6879,18 @@
         <v>1875.8</v>
       </c>
     </row>
-    <row r="134" spans="1:9" s="3" customFormat="1">
+    <row r="134" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E134" s="7">
         <v>37544.519999999997</v>
@@ -6908,18 +6908,18 @@
         <v>42800.76</v>
       </c>
     </row>
-    <row r="135" spans="1:9" s="3" customFormat="1">
+    <row r="135" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E135" s="4">
         <v>2331688.5869999998</v>
@@ -6937,18 +6937,18 @@
         <v>2658124.9879999999</v>
       </c>
     </row>
-    <row r="136" spans="1:9" s="3" customFormat="1">
+    <row r="136" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E136" s="4">
         <v>18248</v>
@@ -6966,18 +6966,18 @@
         <v>20620.240000000002</v>
       </c>
     </row>
-    <row r="137" spans="1:9" s="3" customFormat="1">
+    <row r="137" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E137" s="4">
         <v>8650</v>
@@ -6995,18 +6995,18 @@
         <v>9861</v>
       </c>
     </row>
-    <row r="138" spans="1:9" s="3" customFormat="1">
+    <row r="138" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>799</v>
+        <v>779</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E138" s="4">
         <v>3560</v>
@@ -7024,18 +7024,18 @@
         <v>4022.8</v>
       </c>
     </row>
-    <row r="139" spans="1:9" s="3" customFormat="1">
+    <row r="139" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E139" s="4">
         <v>4500</v>
@@ -7053,18 +7053,18 @@
         <v>5130</v>
       </c>
     </row>
-    <row r="140" spans="1:9" s="3" customFormat="1">
+    <row r="140" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B140" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B140" s="6" t="s">
+      <c r="C140" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C140" s="6" t="s">
-        <v>91</v>
-      </c>
       <c r="D140" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E140" s="7">
         <v>95128.6</v>
@@ -7082,18 +7082,18 @@
         <v>107495.318</v>
       </c>
     </row>
-    <row r="141" spans="1:9" s="3" customFormat="1">
+    <row r="141" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E141" s="4">
         <v>6879.55</v>
@@ -7111,18 +7111,18 @@
         <v>7842.6869999999999</v>
       </c>
     </row>
-    <row r="142" spans="1:9" s="3" customFormat="1">
+    <row r="142" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E142" s="7">
         <v>19866</v>
@@ -7140,18 +7140,18 @@
         <v>22647.24</v>
       </c>
     </row>
-    <row r="143" spans="1:9" s="3" customFormat="1">
+    <row r="143" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E143" s="4">
         <v>5880</v>
@@ -7169,18 +7169,18 @@
         <v>6703.2</v>
       </c>
     </row>
-    <row r="144" spans="1:9" s="3" customFormat="1">
+    <row r="144" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E144" s="7">
         <v>5791.5</v>
@@ -7198,18 +7198,18 @@
         <v>6602.31</v>
       </c>
     </row>
-    <row r="145" spans="1:9" s="3" customFormat="1">
+    <row r="145" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E145" s="4">
         <v>248955.53</v>
@@ -7227,18 +7227,18 @@
         <v>281319.74890000001</v>
       </c>
     </row>
-    <row r="146" spans="1:9" s="3" customFormat="1">
+    <row r="146" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B146" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="C146" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="D146" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="E146" s="4">
         <v>11578.96</v>
@@ -7256,18 +7256,18 @@
         <v>13200.0144</v>
       </c>
     </row>
-    <row r="147" spans="1:9" s="3" customFormat="1">
+    <row r="147" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B147" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="C147" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C147" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D147" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E147" s="4">
         <v>90079.75</v>
@@ -7285,18 +7285,18 @@
         <v>101790.11749999999</v>
       </c>
     </row>
-    <row r="148" spans="1:9" s="3" customFormat="1">
+    <row r="148" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B148" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B148" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="C148" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E148" s="4">
         <v>13080</v>
@@ -7314,18 +7314,18 @@
         <v>14780.4</v>
       </c>
     </row>
-    <row r="149" spans="1:9" s="3" customFormat="1">
+    <row r="149" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E149" s="7">
         <v>323135.96500000003</v>
@@ -7343,18 +7343,18 @@
         <v>368375</v>
       </c>
     </row>
-    <row r="150" spans="1:9" s="3" customFormat="1">
+    <row r="150" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E150" s="7">
         <v>148500</v>
@@ -7372,18 +7372,18 @@
         <v>167805</v>
       </c>
     </row>
-    <row r="151" spans="1:9" s="3" customFormat="1">
+    <row r="151" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>801</v>
+        <v>781</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>802</v>
+        <v>782</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E151" s="7">
         <v>2100</v>
@@ -7401,18 +7401,18 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="152" spans="1:9" s="3" customFormat="1">
+    <row r="152" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B152" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="C152" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="D152" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="E152" s="4">
         <v>70500</v>
@@ -7430,18 +7430,18 @@
         <v>80370</v>
       </c>
     </row>
-    <row r="153" spans="1:9" s="3" customFormat="1">
+    <row r="153" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E153" s="4">
         <v>33000</v>
@@ -7459,18 +7459,18 @@
         <v>37290</v>
       </c>
     </row>
-    <row r="154" spans="1:9" s="3" customFormat="1">
+    <row r="154" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E154" s="4">
         <v>9992</v>
@@ -7488,18 +7488,18 @@
         <v>11390.88</v>
       </c>
     </row>
-    <row r="155" spans="1:9" s="3" customFormat="1">
+    <row r="155" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E155" s="7">
         <v>1433</v>
@@ -7517,18 +7517,18 @@
         <v>1633.62</v>
       </c>
     </row>
-    <row r="156" spans="1:9" s="3" customFormat="1">
+    <row r="156" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E156" s="4">
         <v>40592.523999999998</v>
@@ -7546,18 +7546,18 @@
         <v>46275.474000000002</v>
       </c>
     </row>
-    <row r="157" spans="1:9" s="3" customFormat="1">
+    <row r="157" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E157" s="7">
         <v>2060</v>
@@ -7575,18 +7575,18 @@
         <v>2327.8000000000002</v>
       </c>
     </row>
-    <row r="158" spans="1:9" s="3" customFormat="1">
+    <row r="158" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E158" s="4">
         <v>2750</v>
@@ -7604,18 +7604,18 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="159" spans="1:9" s="3" customFormat="1">
+    <row r="159" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>803</v>
+        <v>783</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>804</v>
+        <v>784</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E159" s="4">
         <v>30545</v>
@@ -7633,18 +7633,18 @@
         <v>34515.85</v>
       </c>
     </row>
-    <row r="160" spans="1:9" s="3" customFormat="1">
+    <row r="160" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>822</v>
+        <v>802</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="E160" s="4">
         <v>17763.157500000001</v>
@@ -7662,18 +7662,18 @@
         <v>20249.99955</v>
       </c>
     </row>
-    <row r="161" spans="1:9" s="3" customFormat="1">
+    <row r="161" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E161" s="7">
         <v>17100</v>
@@ -7691,18 +7691,18 @@
         <v>19323</v>
       </c>
     </row>
-    <row r="162" spans="1:9" s="3" customFormat="1">
+    <row r="162" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E162" s="4">
         <v>12966</v>
@@ -7720,15 +7720,15 @@
         <v>14651.58</v>
       </c>
     </row>
-    <row r="163" spans="1:9" s="3" customFormat="1">
+    <row r="163" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>763</v>
+        <v>743</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>764</v>
+        <v>744</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>14</v>
@@ -7749,18 +7749,18 @@
         <v>12494.4</v>
       </c>
     </row>
-    <row r="164" spans="1:9" s="3" customFormat="1">
+    <row r="164" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E164" s="7">
         <v>117350</v>
@@ -7778,18 +7778,18 @@
         <v>133779</v>
       </c>
     </row>
-    <row r="165" spans="1:9" s="3" customFormat="1">
+    <row r="165" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E165" s="7">
         <v>55016.5</v>
@@ -7807,18 +7807,18 @@
         <v>62168.644999999997</v>
       </c>
     </row>
-    <row r="166" spans="1:9" s="3" customFormat="1">
+    <row r="166" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E166" s="4">
         <v>20550</v>
@@ -7836,18 +7836,18 @@
         <v>23221.5</v>
       </c>
     </row>
-    <row r="167" spans="1:9" s="3" customFormat="1">
+    <row r="167" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E167" s="4">
         <v>11079.2</v>
@@ -7865,18 +7865,18 @@
         <v>12630.288</v>
       </c>
     </row>
-    <row r="168" spans="1:9" s="3" customFormat="1">
+    <row r="168" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E168" s="7">
         <v>1054.58</v>
@@ -7894,18 +7894,18 @@
         <v>1202.221</v>
       </c>
     </row>
-    <row r="169" spans="1:9" s="3" customFormat="1">
+    <row r="169" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E169" s="4">
         <v>26112.06</v>
@@ -7923,18 +7923,18 @@
         <v>29767.7484</v>
       </c>
     </row>
-    <row r="170" spans="1:9" s="3" customFormat="1">
+    <row r="170" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E170" s="7">
         <v>52650</v>
@@ -7952,18 +7952,18 @@
         <v>60021</v>
       </c>
     </row>
-    <row r="171" spans="1:9" s="3" customFormat="1">
+    <row r="171" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E171" s="4">
         <v>3050</v>
@@ -7981,18 +7981,18 @@
         <v>3477</v>
       </c>
     </row>
-    <row r="172" spans="1:9" s="3" customFormat="1">
+    <row r="172" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B172" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B172" s="6" t="s">
+      <c r="C172" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C172" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="D172" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E172" s="7">
         <v>401475</v>
@@ -8010,18 +8010,18 @@
         <v>456333.95</v>
       </c>
     </row>
-    <row r="173" spans="1:9" s="3" customFormat="1">
+    <row r="173" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>817</v>
+        <v>797</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>818</v>
+        <v>798</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>819</v>
+        <v>799</v>
       </c>
       <c r="E173" s="4">
         <v>7800</v>
@@ -8039,18 +8039,18 @@
         <v>8892</v>
       </c>
     </row>
-    <row r="174" spans="1:9" s="3" customFormat="1">
+    <row r="174" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
-        <v>805</v>
+        <v>785</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>806</v>
+        <v>786</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>807</v>
+        <v>787</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E174" s="7">
         <v>450</v>
@@ -8068,18 +8068,18 @@
         <v>508.5</v>
       </c>
     </row>
-    <row r="175" spans="1:9" s="3" customFormat="1">
+    <row r="175" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>809</v>
+        <v>789</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>807</v>
+        <v>787</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E175" s="4">
         <v>950</v>
@@ -8097,18 +8097,18 @@
         <v>1073.5</v>
       </c>
     </row>
-    <row r="176" spans="1:9" s="3" customFormat="1">
+    <row r="176" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E176" s="7">
         <v>120128.5</v>
@@ -8126,18 +8126,18 @@
         <v>136946.49</v>
       </c>
     </row>
-    <row r="177" spans="1:9" s="3" customFormat="1">
+    <row r="177" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E177" s="7">
         <v>25213.5</v>
@@ -8155,18 +8155,18 @@
         <v>28743.39</v>
       </c>
     </row>
-    <row r="178" spans="1:9" s="3" customFormat="1">
+    <row r="178" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B178" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B178" s="3" t="s">
+      <c r="C178" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C178" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="D178" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E178" s="4">
         <v>46525.599999999999</v>
@@ -8184,18 +8184,18 @@
         <v>52573.928</v>
       </c>
     </row>
-    <row r="179" spans="1:9" s="3" customFormat="1">
+    <row r="179" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E179" s="7">
         <v>20877.5</v>
@@ -8213,18 +8213,18 @@
         <v>23800.35</v>
       </c>
     </row>
-    <row r="180" spans="1:9" s="3" customFormat="1">
+    <row r="180" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E180" s="4">
         <v>20969.454000000002</v>
@@ -8242,18 +8242,18 @@
         <v>23905.173999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:9" s="3" customFormat="1">
+    <row r="181" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E181" s="4">
         <v>13620.5</v>
@@ -8271,18 +8271,18 @@
         <v>15527.37</v>
       </c>
     </row>
-    <row r="182" spans="1:9" s="3" customFormat="1">
+    <row r="182" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E182" s="4">
         <v>70980</v>
@@ -8300,18 +8300,18 @@
         <v>70270.2</v>
       </c>
     </row>
-    <row r="183" spans="1:9" s="3" customFormat="1">
+    <row r="183" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E183" s="4">
         <v>652172</v>
@@ -8329,18 +8329,18 @@
         <v>736954.36</v>
       </c>
     </row>
-    <row r="184" spans="1:9" s="3" customFormat="1">
+    <row r="184" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E184" s="7">
         <v>2268.8000000000002</v>
@@ -8358,18 +8358,18 @@
         <v>2586.4319999999998</v>
       </c>
     </row>
-    <row r="185" spans="1:9" s="3" customFormat="1">
+    <row r="185" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E185" s="4">
         <v>307999.28999999998</v>
@@ -8387,18 +8387,18 @@
         <v>348039.19770000002</v>
       </c>
     </row>
-    <row r="186" spans="1:9" s="3" customFormat="1">
+    <row r="186" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B186" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B186" s="6" t="s">
+      <c r="C186" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C186" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="D186" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E186" s="7">
         <v>71710</v>
@@ -8416,18 +8416,18 @@
         <v>81032.3</v>
       </c>
     </row>
-    <row r="187" spans="1:9" s="3" customFormat="1">
+    <row r="187" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E187" s="4">
         <v>1273061.4029999999</v>
@@ -8445,18 +8445,18 @@
         <v>1451290</v>
       </c>
     </row>
-    <row r="188" spans="1:9" s="3" customFormat="1">
+    <row r="188" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E188" s="7">
         <v>913894.73199999996</v>
@@ -8474,18 +8474,18 @@
         <v>1041839.9939999999</v>
       </c>
     </row>
-    <row r="189" spans="1:9" s="3" customFormat="1">
+    <row r="189" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E189" s="4">
         <v>3900</v>
@@ -8503,18 +8503,18 @@
         <v>4407</v>
       </c>
     </row>
-    <row r="190" spans="1:9" s="3" customFormat="1">
+    <row r="190" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B190" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B190" s="3" t="s">
+      <c r="C190" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C190" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="D190" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E190" s="4">
         <v>14500</v>
@@ -8532,18 +8532,18 @@
         <v>16530</v>
       </c>
     </row>
-    <row r="191" spans="1:9" s="3" customFormat="1">
+    <row r="191" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B191" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B191" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="C191" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E191" s="4">
         <v>3415</v>
@@ -8561,18 +8561,18 @@
         <v>3858.95</v>
       </c>
     </row>
-    <row r="192" spans="1:9" s="3" customFormat="1">
+    <row r="192" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E192" s="7">
         <v>5681.25</v>
@@ -8590,18 +8590,18 @@
         <v>6419.8125</v>
       </c>
     </row>
-    <row r="193" spans="1:9" s="3" customFormat="1">
+    <row r="193" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E193" s="7">
         <v>12325</v>
@@ -8619,18 +8619,18 @@
         <v>13927.25</v>
       </c>
     </row>
-    <row r="194" spans="1:9" s="3" customFormat="1">
+    <row r="194" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B194" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B194" s="3" t="s">
+      <c r="C194" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C194" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="D194" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E194" s="4">
         <v>47417</v>
@@ -8648,18 +8648,18 @@
         <v>54055.38</v>
       </c>
     </row>
-    <row r="195" spans="1:9" s="3" customFormat="1">
+    <row r="195" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E195" s="7">
         <v>95650</v>
@@ -8677,18 +8677,18 @@
         <v>109041</v>
       </c>
     </row>
-    <row r="196" spans="1:9" s="3" customFormat="1">
+    <row r="196" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E196" s="4">
         <v>87650</v>
@@ -8706,18 +8706,18 @@
         <v>99921</v>
       </c>
     </row>
-    <row r="197" spans="1:9" s="3" customFormat="1">
+    <row r="197" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E197" s="7">
         <v>54999.875</v>
@@ -8735,18 +8735,18 @@
         <v>62149.858749999999</v>
       </c>
     </row>
-    <row r="198" spans="1:9" s="3" customFormat="1">
+    <row r="198" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="E198" s="4">
         <v>14000</v>
@@ -8764,18 +8764,18 @@
         <v>15750</v>
       </c>
     </row>
-    <row r="199" spans="1:9" s="3" customFormat="1">
+    <row r="199" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E199" s="7">
         <v>5195</v>
@@ -8793,18 +8793,18 @@
         <v>5922.3</v>
       </c>
     </row>
-    <row r="200" spans="1:9" s="3" customFormat="1">
+    <row r="200" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>785</v>
+        <v>765</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>786</v>
+        <v>766</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>787</v>
+        <v>767</v>
       </c>
       <c r="E200" s="4">
         <v>31500</v>
@@ -8822,18 +8822,18 @@
         <v>35595</v>
       </c>
     </row>
-    <row r="201" spans="1:9" s="3" customFormat="1">
+    <row r="201" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
-        <v>788</v>
+        <v>768</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>789</v>
+        <v>769</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>787</v>
+        <v>767</v>
       </c>
       <c r="E201" s="7">
         <v>21820</v>
@@ -8851,18 +8851,18 @@
         <v>24656.6</v>
       </c>
     </row>
-    <row r="202" spans="1:9" s="3" customFormat="1">
+    <row r="202" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E202" s="4">
         <v>2413741.2239999999</v>
@@ -8880,18 +8880,18 @@
         <v>2751664.9950000001</v>
       </c>
     </row>
-    <row r="203" spans="1:9" s="3" customFormat="1">
+    <row r="203" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E203" s="4">
         <v>5017.95</v>
@@ -8909,18 +8909,18 @@
         <v>5720.4629999999997</v>
       </c>
     </row>
-    <row r="204" spans="1:9" s="3" customFormat="1">
+    <row r="204" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
-        <v>751</v>
+        <v>826</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>752</v>
+        <v>734</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E204" s="7">
         <v>9399</v>
@@ -8938,18 +8938,18 @@
         <v>10714.86</v>
       </c>
     </row>
-    <row r="205" spans="1:9" s="3" customFormat="1">
+    <row r="205" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E205" s="7">
         <v>4390.5627999999997</v>
@@ -8967,18 +8967,18 @@
         <v>5005.2428</v>
       </c>
     </row>
-    <row r="206" spans="1:9" s="3" customFormat="1">
+    <row r="206" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B206" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B206" s="6" t="s">
+      <c r="C206" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C206" s="6" t="s">
-        <v>183</v>
-      </c>
       <c r="D206" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E206" s="7">
         <v>18000</v>
@@ -8996,18 +8996,18 @@
         <v>20520</v>
       </c>
     </row>
-    <row r="207" spans="1:9" s="3" customFormat="1">
+    <row r="207" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E207" s="4">
         <v>19700</v>
@@ -9025,18 +9025,18 @@
         <v>22261</v>
       </c>
     </row>
-    <row r="208" spans="1:9" s="3" customFormat="1">
+    <row r="208" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E208" s="7">
         <v>30000</v>
@@ -9054,18 +9054,18 @@
         <v>34200</v>
       </c>
     </row>
-    <row r="209" spans="1:9" s="3" customFormat="1">
+    <row r="209" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E209" s="7">
         <v>9681.75</v>
@@ -9083,18 +9083,18 @@
         <v>11037.195</v>
       </c>
     </row>
-    <row r="210" spans="1:9" s="3" customFormat="1">
+    <row r="210" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B210" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B210" s="6" t="s">
+      <c r="C210" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C210" s="6" t="s">
-        <v>121</v>
-      </c>
       <c r="D210" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E210" s="7">
         <v>12209</v>
@@ -9112,18 +9112,18 @@
         <v>13796.17</v>
       </c>
     </row>
-    <row r="211" spans="1:9" s="3" customFormat="1">
+    <row r="211" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B211" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B211" s="6" t="s">
-        <v>147</v>
-      </c>
       <c r="C211" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E211" s="7">
         <v>200000</v>
@@ -9141,18 +9141,18 @@
         <v>228000</v>
       </c>
     </row>
-    <row r="212" spans="1:9" s="3" customFormat="1">
+    <row r="212" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E212" s="4">
         <v>4500</v>
@@ -9170,18 +9170,18 @@
         <v>5085</v>
       </c>
     </row>
-    <row r="213" spans="1:9" s="3" customFormat="1">
+    <row r="213" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E213" s="7">
         <v>987157.89599999995</v>
@@ -9199,18 +9199,18 @@
         <v>1125360.0009999999</v>
       </c>
     </row>
-    <row r="214" spans="1:9" s="3" customFormat="1">
+    <row r="214" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>790</v>
+        <v>770</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>791</v>
+        <v>771</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>781</v>
+        <v>761</v>
       </c>
       <c r="E214" s="4">
         <v>19040</v>
@@ -9228,18 +9228,18 @@
         <v>21705.599999999999</v>
       </c>
     </row>
-    <row r="215" spans="1:9" s="3" customFormat="1">
+    <row r="215" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>826</v>
+        <v>806</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="E215" s="7">
         <v>4736.8419999999996</v>
@@ -9257,7 +9257,7 @@
         <v>5399.9998800000003</v>
       </c>
     </row>
-    <row r="216" spans="1:9" s="3" customFormat="1">
+    <row r="216" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
         <v>29</v>
       </c>
@@ -9286,7 +9286,7 @@
         <v>120298.5</v>
       </c>
     </row>
-    <row r="217" spans="1:9" s="3" customFormat="1">
+    <row r="217" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
         <v>33</v>
       </c>
@@ -9315,18 +9315,18 @@
         <v>13338</v>
       </c>
     </row>
-    <row r="218" spans="1:9" s="3" customFormat="1">
+    <row r="218" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="E218" s="4">
         <v>480</v>
@@ -9344,18 +9344,18 @@
         <v>547.20000000000005</v>
       </c>
     </row>
-    <row r="219" spans="1:9" s="3" customFormat="1">
+    <row r="219" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E219" s="4">
         <v>17000</v>
@@ -9373,18 +9373,18 @@
         <v>19380</v>
       </c>
     </row>
-    <row r="220" spans="1:9" s="3" customFormat="1">
+    <row r="220" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E220" s="7">
         <v>53425</v>
@@ -9402,18 +9402,18 @@
         <v>60904.5</v>
       </c>
     </row>
-    <row r="221" spans="1:9" s="3" customFormat="1">
+    <row r="221" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E221" s="4">
         <v>11777</v>
@@ -9431,18 +9431,18 @@
         <v>13425.78</v>
       </c>
     </row>
-    <row r="222" spans="1:9" s="3" customFormat="1">
+    <row r="222" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E222" s="7">
         <v>73313</v>
@@ -9460,18 +9460,18 @@
         <v>83576.820000000007</v>
       </c>
     </row>
-    <row r="223" spans="1:9" s="3" customFormat="1">
+    <row r="223" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E223" s="4">
         <v>43398</v>
@@ -9489,18 +9489,18 @@
         <v>49039.74</v>
       </c>
     </row>
-    <row r="224" spans="1:9" s="3" customFormat="1">
+    <row r="224" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E224" s="4">
         <v>75765</v>
@@ -9518,18 +9518,18 @@
         <v>86372.1</v>
       </c>
     </row>
-    <row r="225" spans="1:9" s="3" customFormat="1">
+    <row r="225" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>810</v>
+        <v>790</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E225" s="7">
         <v>2750</v>
@@ -9547,7 +9547,7 @@
         <v>3107.5</v>
       </c>
     </row>
-    <row r="226" spans="1:9" s="3" customFormat="1">
+    <row r="226" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
         <v>35</v>
       </c>
@@ -9576,7 +9576,7 @@
         <v>225492</v>
       </c>
     </row>
-    <row r="227" spans="1:9" s="3" customFormat="1">
+    <row r="227" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
         <v>38</v>
       </c>
@@ -9605,18 +9605,18 @@
         <v>35197.340400000001</v>
       </c>
     </row>
-    <row r="228" spans="1:9" s="3" customFormat="1">
+    <row r="228" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E228" s="4">
         <v>19250</v>
@@ -9634,18 +9634,18 @@
         <v>21945</v>
       </c>
     </row>
-    <row r="229" spans="1:9" s="3" customFormat="1">
+    <row r="229" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E229" s="7">
         <v>5750</v>
@@ -9663,18 +9663,18 @@
         <v>6497.5</v>
       </c>
     </row>
-    <row r="230" spans="1:9" s="3" customFormat="1">
+    <row r="230" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="E230" s="7">
         <v>20800</v>
@@ -9692,18 +9692,18 @@
         <v>23712</v>
       </c>
     </row>
-    <row r="231" spans="1:9" s="3" customFormat="1">
+    <row r="231" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E231" s="4">
         <v>15935.5</v>
@@ -9721,18 +9721,18 @@
         <v>18166.47</v>
       </c>
     </row>
-    <row r="232" spans="1:9" s="3" customFormat="1">
+    <row r="232" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E232" s="7">
         <v>93366</v>
@@ -9750,18 +9750,18 @@
         <v>106437.24</v>
       </c>
     </row>
-    <row r="233" spans="1:9" s="3" customFormat="1">
+    <row r="233" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="E233" s="4">
         <v>16900</v>
@@ -9779,18 +9779,18 @@
         <v>19266</v>
       </c>
     </row>
-    <row r="234" spans="1:9" s="3" customFormat="1">
+    <row r="234" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>811</v>
+        <v>791</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E234" s="4">
         <v>11750</v>
@@ -9808,18 +9808,18 @@
         <v>13277.5</v>
       </c>
     </row>
-    <row r="235" spans="1:9" s="3" customFormat="1">
+    <row r="235" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>813</v>
+        <v>793</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="E235" s="7">
         <v>450</v>
@@ -9837,18 +9837,18 @@
         <v>508.5</v>
       </c>
     </row>
-    <row r="236" spans="1:9" s="3" customFormat="1">
+    <row r="236" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>589</v>
+        <v>830</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E236" s="4">
         <v>3430</v>
@@ -9866,18 +9866,18 @@
         <v>3910.2</v>
       </c>
     </row>
-    <row r="237" spans="1:9" s="3" customFormat="1">
+    <row r="237" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B237" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B237" s="6" t="s">
+      <c r="C237" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C237" s="6" t="s">
-        <v>210</v>
-      </c>
       <c r="D237" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E237" s="7">
         <v>8500</v>
@@ -9895,18 +9895,18 @@
         <v>9605</v>
       </c>
     </row>
-    <row r="238" spans="1:9" s="3" customFormat="1">
+    <row r="238" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E238" s="7">
         <v>15190</v>
@@ -9924,7 +9924,7 @@
         <v>17164.7</v>
       </c>
     </row>
-    <row r="239" spans="1:9" s="3" customFormat="1">
+    <row r="239" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>43</v>
       </c>
@@ -9953,18 +9953,18 @@
         <v>52034.16</v>
       </c>
     </row>
-    <row r="240" spans="1:9" s="3" customFormat="1">
+    <row r="240" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>45</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E240" s="7">
         <v>365560</v>
@@ -9982,12 +9982,12 @@
         <v>413082.8</v>
       </c>
     </row>
-    <row r="241" spans="1:9" s="3" customFormat="1">
+    <row r="241" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6" t="s">
-        <v>767</v>
+        <v>747</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>768</v>
+        <v>748</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>45</v>
@@ -10011,18 +10011,18 @@
         <v>32444.400000000001</v>
       </c>
     </row>
-    <row r="242" spans="1:9" s="3" customFormat="1">
+    <row r="242" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E242" s="4">
         <v>16399</v>
@@ -10040,18 +10040,18 @@
         <v>18694.86</v>
       </c>
     </row>
-    <row r="243" spans="1:9" s="3" customFormat="1">
+    <row r="243" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E243" s="4">
         <v>3680</v>
@@ -10069,18 +10069,18 @@
         <v>4195.2</v>
       </c>
     </row>
-    <row r="244" spans="1:9" s="3" customFormat="1">
+    <row r="244" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>772</v>
+        <v>752</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
       <c r="E244" s="7">
         <v>9500</v>
@@ -10098,7 +10098,7 @@
         <v>10830</v>
       </c>
     </row>
-    <row r="245" spans="1:9" s="3" customFormat="1">
+    <row r="245" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6" t="s">
         <v>40</v>
       </c>
@@ -10127,18 +10127,18 @@
         <v>23028</v>
       </c>
     </row>
-    <row r="246" spans="1:9" s="3" customFormat="1">
+    <row r="246" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B246" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="B246" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E246" s="4">
         <v>77550</v>
@@ -10156,18 +10156,18 @@
         <v>88407</v>
       </c>
     </row>
-    <row r="247" spans="1:9" s="3" customFormat="1">
+    <row r="247" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C247" s="6" t="s">
         <v>42</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E247" s="7">
         <v>17500</v>
@@ -10185,18 +10185,18 @@
         <v>19950</v>
       </c>
     </row>
-    <row r="248" spans="1:9" s="3" customFormat="1">
+    <row r="248" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E248" s="4">
         <v>15327</v>
@@ -10214,18 +10214,18 @@
         <v>17472.78</v>
       </c>
     </row>
-    <row r="249" spans="1:9" s="3" customFormat="1">
+    <row r="249" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B249" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B249" s="3" t="s">
+      <c r="C249" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C249" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="D249" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E249" s="4">
         <v>2140</v>
@@ -10243,18 +10243,18 @@
         <v>2418.1999999999998</v>
       </c>
     </row>
-    <row r="250" spans="1:9" s="3" customFormat="1">
+    <row r="250" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E250" s="4">
         <v>1200</v>
@@ -10272,18 +10272,18 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="251" spans="1:9" s="3" customFormat="1">
+    <row r="251" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B251" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B251" s="3" t="s">
+      <c r="C251" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C251" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D251" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E251" s="4">
         <v>152854</v>
@@ -10301,18 +10301,18 @@
         <v>172725.02</v>
       </c>
     </row>
-    <row r="252" spans="1:9" s="3" customFormat="1">
+    <row r="252" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E252" s="7">
         <v>11700</v>
@@ -10330,18 +10330,18 @@
         <v>13221</v>
       </c>
     </row>
-    <row r="253" spans="1:9" s="3" customFormat="1">
+    <row r="253" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E253" s="4">
         <v>11775</v>
@@ -10359,18 +10359,18 @@
         <v>13305.75</v>
       </c>
     </row>
-    <row r="254" spans="1:9" s="3" customFormat="1">
+    <row r="254" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E254" s="7">
         <v>439994.37</v>
@@ -10388,18 +10388,18 @@
         <v>497193.63809999998</v>
       </c>
     </row>
-    <row r="255" spans="1:9" s="3" customFormat="1">
+    <row r="255" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E255" s="7">
         <v>21540.7</v>
@@ -10417,18 +10417,18 @@
         <v>24556.398000000001</v>
       </c>
     </row>
-    <row r="256" spans="1:9" s="3" customFormat="1">
+    <row r="256" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B256" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B256" s="6" t="s">
+      <c r="C256" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C256" s="6" t="s">
+      <c r="D256" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="D256" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="E256" s="7">
         <v>4290</v>
@@ -10446,18 +10446,18 @@
         <v>4847.7</v>
       </c>
     </row>
-    <row r="257" spans="1:9" s="3" customFormat="1">
+    <row r="257" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="E257" s="4">
         <v>27475</v>
@@ -10475,18 +10475,18 @@
         <v>31125.5</v>
       </c>
     </row>
-    <row r="258" spans="1:9" s="3" customFormat="1">
+    <row r="258" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>222</v>
+        <v>832</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E258" s="4">
         <v>6960</v>
@@ -10504,18 +10504,18 @@
         <v>7864.8</v>
       </c>
     </row>
-    <row r="259" spans="1:9" s="3" customFormat="1">
+    <row r="259" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B259" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B259" s="6" t="s">
+      <c r="C259" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C259" s="6" t="s">
-        <v>109</v>
-      </c>
       <c r="D259" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E259" s="7">
         <v>85878.2</v>
@@ -10533,7 +10533,7 @@
         <v>97042.365999999995</v>
       </c>
     </row>
-    <row r="260" spans="1:9" s="3" customFormat="1">
+    <row r="260" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
         <v>26</v>
       </c>
@@ -10562,18 +10562,18 @@
         <v>44070</v>
       </c>
     </row>
-    <row r="261" spans="1:9" s="3" customFormat="1">
+    <row r="261" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C261" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E261" s="7">
         <v>30100</v>
@@ -10591,18 +10591,18 @@
         <v>29799</v>
       </c>
     </row>
-    <row r="262" spans="1:9" s="3" customFormat="1">
+    <row r="262" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B262" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B262" s="3" t="s">
+      <c r="C262" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C262" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="D262" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E262" s="4">
         <v>83375</v>
@@ -10620,18 +10620,18 @@
         <v>94213.75</v>
       </c>
     </row>
-    <row r="263" spans="1:9" s="3" customFormat="1">
+    <row r="263" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6" t="s">
-        <v>225</v>
+        <v>833</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E263" s="7">
         <v>800</v>
@@ -10649,18 +10649,18 @@
         <v>904</v>
       </c>
     </row>
-    <row r="264" spans="1:9" s="3" customFormat="1">
+    <row r="264" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E264" s="4">
         <v>93475.91</v>
@@ -10678,18 +10678,18 @@
         <v>105627.77830000001</v>
       </c>
     </row>
-    <row r="265" spans="1:9" s="3" customFormat="1">
+    <row r="265" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E265" s="4">
         <v>13513.5</v>
@@ -10707,18 +10707,18 @@
         <v>15405.39</v>
       </c>
     </row>
-    <row r="266" spans="1:9" s="3" customFormat="1">
+    <row r="266" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E266" s="7">
         <v>38083.5</v>
@@ -10736,18 +10736,18 @@
         <v>43415.19</v>
       </c>
     </row>
-    <row r="267" spans="1:9" s="3" customFormat="1">
+    <row r="267" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E267" s="4">
         <v>8750</v>
@@ -10765,18 +10765,18 @@
         <v>9887.5</v>
       </c>
     </row>
-    <row r="268" spans="1:9" s="3" customFormat="1">
+    <row r="268" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E268" s="4">
         <v>29150</v>
@@ -10794,18 +10794,18 @@
         <v>33231</v>
       </c>
     </row>
-    <row r="269" spans="1:9" s="3" customFormat="1">
+    <row r="269" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B269" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B269" s="6" t="s">
+      <c r="C269" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C269" s="6" t="s">
+      <c r="D269" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="D269" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="E269" s="7">
         <v>13230</v>
@@ -10823,18 +10823,18 @@
         <v>15082.2</v>
       </c>
     </row>
-    <row r="270" spans="1:9" s="3" customFormat="1">
+    <row r="270" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B270" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B270" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="C270" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E270" s="7">
         <v>155100</v>
@@ -10852,18 +10852,18 @@
         <v>176814</v>
       </c>
     </row>
-    <row r="271" spans="1:9" s="3" customFormat="1">
+    <row r="271" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E271" s="4">
         <v>11030</v>
@@ -10881,18 +10881,18 @@
         <v>12574.2</v>
       </c>
     </row>
-    <row r="272" spans="1:9" s="3" customFormat="1">
+    <row r="272" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E272" s="7">
         <v>87525</v>
@@ -10910,18 +10910,18 @@
         <v>99778.5</v>
       </c>
     </row>
-    <row r="273" spans="1:9" s="3" customFormat="1">
+    <row r="273" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E273" s="4">
         <v>42050</v>
@@ -10939,18 +10939,18 @@
         <v>47937</v>
       </c>
     </row>
-    <row r="274" spans="1:9" s="3" customFormat="1">
+    <row r="274" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E274" s="7">
         <v>54100</v>
@@ -10968,18 +10968,18 @@
         <v>61674</v>
       </c>
     </row>
-    <row r="275" spans="1:9" s="3" customFormat="1">
+    <row r="275" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E275" s="7">
         <v>16201.8</v>
@@ -10997,18 +10997,18 @@
         <v>18470.052</v>
       </c>
     </row>
-    <row r="276" spans="1:9" s="3" customFormat="1">
+    <row r="276" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E276" s="4">
         <v>6938.1</v>
@@ -11026,18 +11026,18 @@
         <v>7909.4340000000002</v>
       </c>
     </row>
-    <row r="277" spans="1:9" s="3" customFormat="1">
+    <row r="277" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E277" s="7">
         <v>12500</v>
@@ -11055,18 +11055,18 @@
         <v>14125</v>
       </c>
     </row>
-    <row r="278" spans="1:9" s="3" customFormat="1">
+    <row r="278" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E278" s="7">
         <v>15030</v>
@@ -11084,18 +11084,18 @@
         <v>16983.900000000001</v>
       </c>
     </row>
-    <row r="279" spans="1:9" s="3" customFormat="1">
+    <row r="279" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E279" s="7">
         <v>25600</v>
@@ -11113,18 +11113,18 @@
         <v>28928</v>
       </c>
     </row>
-    <row r="280" spans="1:9" s="3" customFormat="1">
+    <row r="280" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="E280" s="4">
         <v>115266.2056</v>
@@ -11142,18 +11142,18 @@
         <v>130250.81232</v>
       </c>
     </row>
-    <row r="281" spans="1:9" s="3" customFormat="1">
+    <row r="281" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E281" s="4">
         <v>409873</v>
@@ -11171,15 +11171,15 @@
         <v>463156.49</v>
       </c>
     </row>
-    <row r="282" spans="1:9" s="3" customFormat="1">
+    <row r="282" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
-        <v>769</v>
+        <v>749</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>14</v>
@@ -11200,18 +11200,18 @@
         <v>19676.400000000001</v>
       </c>
     </row>
-    <row r="283" spans="1:9" s="3" customFormat="1">
+    <row r="283" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E283" s="4">
         <v>28695.45</v>
@@ -11229,18 +11229,18 @@
         <v>32712.812999999998</v>
       </c>
     </row>
-    <row r="284" spans="1:9" s="3" customFormat="1">
+    <row r="284" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E284" s="7">
         <v>70200</v>
@@ -11258,18 +11258,18 @@
         <v>80028</v>
       </c>
     </row>
-    <row r="285" spans="1:9" s="3" customFormat="1">
+    <row r="285" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E285" s="4">
         <v>10588.5</v>
@@ -11287,18 +11287,18 @@
         <v>12070.89</v>
       </c>
     </row>
-    <row r="286" spans="1:9" s="3" customFormat="1">
+    <row r="286" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E286" s="7">
         <v>7699.3</v>
@@ -11316,18 +11316,18 @@
         <v>8777.2019999999993</v>
       </c>
     </row>
-    <row r="287" spans="1:9" s="3" customFormat="1">
+    <row r="287" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B287" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B287" s="6" t="s">
+      <c r="C287" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C287" s="6" t="s">
-        <v>115</v>
-      </c>
       <c r="D287" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E287" s="7">
         <v>43430</v>
@@ -11345,18 +11345,18 @@
         <v>49075.9</v>
       </c>
     </row>
-    <row r="288" spans="1:9" s="3" customFormat="1">
+    <row r="288" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E288" s="4">
         <v>3097.55</v>
@@ -11374,18 +11374,18 @@
         <v>3531.2069999999999</v>
       </c>
     </row>
-    <row r="289" spans="1:9" s="3" customFormat="1">
+    <row r="289" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
       <c r="E289" s="4">
         <v>2250</v>
@@ -11403,18 +11403,18 @@
         <v>2565</v>
       </c>
     </row>
-    <row r="290" spans="1:9" s="3" customFormat="1">
+    <row r="290" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B290" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B290" s="6" t="s">
+      <c r="C290" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C290" s="6" t="s">
+      <c r="D290" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="D290" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="E290" s="7">
         <v>50225</v>
@@ -11432,18 +11432,18 @@
         <v>55749.75</v>
       </c>
     </row>
-    <row r="291" spans="1:9" s="3" customFormat="1">
+    <row r="291" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E291" s="4">
         <v>42808.088000000003</v>
@@ -11461,18 +11461,18 @@
         <v>46361.159299999999</v>
       </c>
     </row>
-    <row r="292" spans="1:9" s="3" customFormat="1">
+    <row r="292" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="E292" s="4">
         <v>2105.2631000000001</v>
@@ -11490,18 +11490,18 @@
         <v>2399.9999299999999</v>
       </c>
     </row>
-    <row r="293" spans="1:9" s="3" customFormat="1">
+    <row r="293" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E293" s="4">
         <v>2351250</v>
@@ -11519,18 +11519,18 @@
         <v>2656912.5</v>
       </c>
     </row>
-    <row r="294" spans="1:9" s="3" customFormat="1">
+    <row r="294" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E294" s="4">
         <v>30550</v>
@@ -11548,18 +11548,18 @@
         <v>34827</v>
       </c>
     </row>
-    <row r="295" spans="1:9" s="3" customFormat="1">
+    <row r="295" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E295" s="4">
         <v>1453.4133999999999</v>
@@ -11577,18 +11577,18 @@
         <v>1656.8933999999999</v>
       </c>
     </row>
-    <row r="296" spans="1:9" s="3" customFormat="1">
+    <row r="296" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E296" s="4">
         <v>1200</v>
@@ -11606,18 +11606,18 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="297" spans="1:9" s="3" customFormat="1">
+    <row r="297" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E297" s="7">
         <v>31500</v>
@@ -11635,18 +11635,18 @@
         <v>35910</v>
       </c>
     </row>
-    <row r="298" spans="1:9" s="3" customFormat="1">
+    <row r="298" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="B298" s="6" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="E298" s="7">
         <v>40142</v>
@@ -11664,18 +11664,18 @@
         <v>45360.46</v>
       </c>
     </row>
-    <row r="299" spans="1:9" s="3" customFormat="1">
+    <row r="299" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="B299" s="6" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E299" s="7">
         <v>25967.99</v>
@@ -11693,18 +11693,18 @@
         <v>29603.508600000001</v>
       </c>
     </row>
-    <row r="300" spans="1:9" s="3" customFormat="1">
+    <row r="300" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E300" s="4">
         <v>68446.899999999994</v>
@@ -11722,18 +11722,18 @@
         <v>78029.466</v>
       </c>
     </row>
-    <row r="301" spans="1:9" s="3" customFormat="1">
+    <row r="301" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E301" s="7">
         <v>221978.68</v>
@@ -11751,18 +11751,18 @@
         <v>250835.90839999999</v>
       </c>
     </row>
-    <row r="302" spans="1:9" s="3" customFormat="1">
+    <row r="302" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E302" s="4">
         <v>14625</v>
@@ -11780,18 +11780,18 @@
         <v>16526.25</v>
       </c>
     </row>
-    <row r="303" spans="1:9" s="3" customFormat="1">
+    <row r="303" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E303" s="4">
         <v>48600</v>
@@ -11809,18 +11809,18 @@
         <v>55404</v>
       </c>
     </row>
-    <row r="304" spans="1:9" s="3" customFormat="1">
+    <row r="304" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B304" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E304" s="7">
         <v>333725</v>
@@ -11838,18 +11838,18 @@
         <v>380446.5</v>
       </c>
     </row>
-    <row r="305" spans="1:9" s="3" customFormat="1">
+    <row r="305" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B305" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E305" s="7">
         <v>15412.5</v>
@@ -11867,18 +11867,18 @@
         <v>17416.125</v>
       </c>
     </row>
-    <row r="306" spans="1:9" s="3" customFormat="1">
+    <row r="306" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B306" s="6" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E306" s="7">
         <v>7875</v>
@@ -11896,18 +11896,18 @@
         <v>8898.75</v>
       </c>
     </row>
-    <row r="307" spans="1:9" s="3" customFormat="1">
+    <row r="307" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="E307" s="7">
         <v>27475</v>
@@ -11925,18 +11925,18 @@
         <v>31321.5</v>
       </c>
     </row>
-    <row r="308" spans="1:9" s="3" customFormat="1">
+    <row r="308" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D308" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E308" s="7">
         <v>16965</v>
@@ -11954,7 +11954,7 @@
         <v>19340.099999999999</v>
       </c>
     </row>
-    <row r="309" spans="1:9" s="3" customFormat="1">
+    <row r="309" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="6" t="s">
         <v>46</v>
       </c>
@@ -11983,18 +11983,18 @@
         <v>228496.47</v>
       </c>
     </row>
-    <row r="310" spans="1:9" s="3" customFormat="1">
+    <row r="310" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="E310" s="4">
         <v>2500</v>
@@ -12012,18 +12012,18 @@
         <v>2825</v>
       </c>
     </row>
-    <row r="311" spans="1:9" s="3" customFormat="1">
+    <row r="311" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E311" s="4">
         <v>26939.25</v>
@@ -12041,18 +12041,18 @@
         <v>30710.744999999999</v>
       </c>
     </row>
-    <row r="312" spans="1:9" s="3" customFormat="1">
+    <row r="312" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E312" s="4">
         <v>136000</v>
@@ -12070,18 +12070,18 @@
         <v>134640</v>
       </c>
     </row>
-    <row r="313" spans="1:9" s="3" customFormat="1">
+    <row r="313" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E313" s="4">
         <v>66000</v>
@@ -12099,18 +12099,18 @@
         <v>75240</v>
       </c>
     </row>
-    <row r="314" spans="1:9" s="3" customFormat="1">
+    <row r="314" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="D314" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E314" s="7">
         <v>22632.240000000002</v>
@@ -12128,18 +12128,18 @@
         <v>25800.7536</v>
       </c>
     </row>
-    <row r="315" spans="1:9" s="3" customFormat="1">
+    <row r="315" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
-        <v>782</v>
+        <v>762</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>783</v>
+        <v>763</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>784</v>
+        <v>764</v>
       </c>
       <c r="E315" s="4">
         <v>1300</v>
@@ -12157,18 +12157,18 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="316" spans="1:9" s="3" customFormat="1">
+    <row r="316" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E316" s="4">
         <v>6700</v>
@@ -12186,18 +12186,18 @@
         <v>7571</v>
       </c>
     </row>
-    <row r="317" spans="1:9" s="3" customFormat="1">
+    <row r="317" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="6" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D317" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E317" s="7">
         <v>69000</v>
@@ -12215,18 +12215,18 @@
         <v>78660</v>
       </c>
     </row>
-    <row r="318" spans="1:9" s="3" customFormat="1">
+    <row r="318" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D318" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E318" s="7">
         <v>12975</v>
@@ -12244,18 +12244,18 @@
         <v>14791.5</v>
       </c>
     </row>
-    <row r="319" spans="1:9" s="3" customFormat="1">
+    <row r="319" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="6" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B319" s="6" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D319" s="6" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E319" s="7">
         <v>354561.31900000002</v>
@@ -12273,18 +12273,18 @@
         <v>400654.29047000001</v>
       </c>
     </row>
-    <row r="320" spans="1:9" s="3" customFormat="1">
+    <row r="320" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E320" s="4">
         <v>60983.75</v>
@@ -12302,18 +12302,18 @@
         <v>69521.47</v>
       </c>
     </row>
-    <row r="321" spans="1:9" s="3" customFormat="1">
+    <row r="321" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D321" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E321" s="7">
         <v>38514</v>
@@ -12331,18 +12331,18 @@
         <v>43520.82</v>
       </c>
     </row>
-    <row r="322" spans="1:9" s="3" customFormat="1">
+    <row r="322" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="3" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E322" s="4">
         <v>23084.1</v>
@@ -12360,18 +12360,18 @@
         <v>26315.874</v>
       </c>
     </row>
-    <row r="323" spans="1:9" s="3" customFormat="1">
+    <row r="323" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="6" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D323" s="6" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E323" s="7">
         <v>3081</v>
@@ -12389,18 +12389,18 @@
         <v>3512.34</v>
       </c>
     </row>
-    <row r="324" spans="1:9" s="3" customFormat="1">
+    <row r="324" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B324" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B324" s="6" t="s">
+      <c r="C324" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="C324" s="6" t="s">
-        <v>216</v>
-      </c>
       <c r="D324" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E324" s="7">
         <v>4000</v>
@@ -12418,18 +12418,18 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="325" spans="1:9" s="3" customFormat="1">
+    <row r="325" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B325" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B325" s="3" t="s">
+      <c r="C325" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C325" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="D325" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E325" s="4">
         <v>44209.8</v>
@@ -12447,9 +12447,9 @@
         <v>49957.074000000001</v>
       </c>
     </row>
-    <row r="326" spans="1:9" s="9" customFormat="1">
+    <row r="326" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="10" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="E326" s="11">
         <f>SUM(E2:E325)</f>
@@ -12486,29 +12486,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="12" customFormat="1">
+    <row r="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>830</v>
+        <v>810</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>832</v>
+        <v>812</v>
       </c>
       <c r="B2">
         <v>346</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -12516,7 +12516,7 @@
         <v>29530495.437200002</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -12524,7 +12524,7 @@
         <v>4575.8044</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -12540,7 +12540,7 @@
         <v>4069646.1832900029</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>135686.92710000003</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -12556,7 +12556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -12564,9 +12564,9 @@
         <v>33459878.881989993</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>833</v>
+        <v>813</v>
       </c>
       <c r="B10">
         <v>1</v>

--- a/data/invoices/totals.xlsx
+++ b/data/invoices/totals.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6160FED9-4F24-4E24-A06E-A2925FCC5166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFC2B88-9DE3-4E18-8A95-3659146753C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="الفواتير 2026-09-01 14-54" sheetId="1" r:id="rId1"/>
+    <sheet name="الفواتير 2026-09-07 10-53" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -208,7 +208,7 @@
     <t>2026-01-13</t>
   </si>
   <si>
-    <t>دنيا العوازال رقم الفاتورة 12.pdf</t>
+    <t>دنيا العوازل رقم الفاتورة 12.pdf</t>
   </si>
   <si>
     <t>12</t>
@@ -679,7 +679,7 @@
     <t>59753</t>
   </si>
   <si>
-    <t>دنيا العوازال رقم الفاتورة 60.pdf</t>
+    <t>دنيا العوازل رقم الفاتورة 60.pdf</t>
   </si>
   <si>
     <t>60</t>
@@ -1729,7 +1729,7 @@
     <t>FR003884-26</t>
   </si>
   <si>
-    <t>دنيا العوازال رقم الفاتورة 141.pdf</t>
+    <t>دنيا العوازل رقم الفاتورة 141.pdf</t>
   </si>
   <si>
     <t>2026-04-29</t>
